--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.63414653176426</v>
+        <v>6.765548811411692</v>
       </c>
       <c r="D2" t="n">
-        <v>41.72682434972281</v>
+        <v>6.780608956829957</v>
       </c>
       <c r="E2" t="n">
-        <v>13.99534034388165</v>
+        <v>2.274242805880768</v>
       </c>
       <c r="F2" t="n">
-        <v>15.04953386823958</v>
+        <v>2.445549253588933</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.72528150315534</v>
+        <v>2.555358244262742</v>
       </c>
       <c r="D3" t="n">
-        <v>14.91270294894116</v>
+        <v>2.423314229202939</v>
       </c>
       <c r="E3" t="n">
-        <v>13.99534034388165</v>
+        <v>2.274242805880768</v>
       </c>
       <c r="F3" t="n">
-        <v>15.04953386823958</v>
+        <v>2.445549253588933</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.52221125911042</v>
+        <v>3.659859329605443</v>
       </c>
       <c r="D4" t="n">
-        <v>17.58550539506897</v>
+        <v>2.857644626698709</v>
       </c>
       <c r="E4" t="n">
-        <v>13.99534034388165</v>
+        <v>2.274242805880768</v>
       </c>
       <c r="F4" t="n">
-        <v>15.04953386823958</v>
+        <v>2.445549253588933</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.94352700562466</v>
+        <v>8.115823138414008</v>
       </c>
       <c r="D5" t="n">
-        <v>50.71025360417797</v>
+        <v>8.240416210678921</v>
       </c>
       <c r="E5" t="n">
-        <v>13.99534034388165</v>
+        <v>2.274242805880768</v>
       </c>
       <c r="F5" t="n">
-        <v>15.04953386823958</v>
+        <v>2.445549253588933</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.49110735921457</v>
+        <v>8.529804945872367</v>
       </c>
       <c r="D6" t="n">
-        <v>32.81967059366185</v>
+        <v>5.333196471470051</v>
       </c>
       <c r="E6" t="n">
-        <v>13.99534034388165</v>
+        <v>2.274242805880768</v>
       </c>
       <c r="F6" t="n">
-        <v>15.04953386823958</v>
+        <v>2.445549253588933</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.58964553270076</v>
+        <v>7.570817399063873</v>
       </c>
       <c r="D7" t="n">
-        <v>9.239677889925522</v>
+        <v>1.501447657112897</v>
       </c>
       <c r="E7" t="n">
-        <v>13.99534034388165</v>
+        <v>2.274242805880768</v>
       </c>
       <c r="F7" t="n">
-        <v>15.04953386823958</v>
+        <v>2.445549253588933</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
